--- a/docs/ВКр магистр/источники.xlsx
+++ b/docs/ВКр магистр/источники.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pa-ga\Desktop\pagamov_bot\docs\ВКр магистр\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6BC6AC26-52B9-492D-86E8-630D4F50FDC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{031A71BF-4629-4F03-9F5A-B2822A0FFAF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="3150" windowWidth="38640" windowHeight="21240" xr2:uid="{0D969096-2410-4963-B90D-99F31EACA825}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="37210" windowHeight="21820" xr2:uid="{0D969096-2410-4963-B90D-99F31EACA825}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -1163,7 +1163,7 @@
   <dimension ref="A1:F42"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.7265625" style="6"/>
+    <col min="1" max="1" width="24.90625" style="6" customWidth="1"/>
     <col min="2" max="2" width="67.08984375" style="6" bestFit="1" customWidth="1"/>
     <col min="3" max="5" width="8.7265625" style="6"/>
     <col min="6" max="6" width="58.1796875" style="6" bestFit="1" customWidth="1"/>
@@ -1372,7 +1372,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="33" spans="6:6" ht="54" x14ac:dyDescent="0.35">
+    <row r="33" spans="6:6" ht="36" x14ac:dyDescent="0.35">
       <c r="F33" s="2" t="s">
         <v>43</v>
       </c>
